--- a/AAII_Financials/Quarterly/OCDDY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/OCDDY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="403" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="445" uniqueCount="92">
   <si>
     <t>OCDDY</t>
   </si>
@@ -656,82 +656,90 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="10" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="12" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46173</v>
+      </c>
+      <c r="E7" s="2">
+        <v>46081</v>
+      </c>
+      <c r="F7" s="2">
         <v>45991</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45900</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45809</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45717</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45627</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45536</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45445</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45353</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>45263</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>45172</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>45074</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44985</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44892</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44800</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -777,8 +785,14 @@
       <c r="Q8" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -824,8 +838,14 @@
       <c r="Q9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -871,8 +891,14 @@
       <c r="Q10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -890,8 +916,10 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -937,8 +965,14 @@
       <c r="Q12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -984,8 +1018,14 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+      <c r="S13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1031,8 +1071,14 @@
       <c r="Q14" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1078,8 +1124,14 @@
       <c r="Q15" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S15" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1094,8 +1146,10 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1141,8 +1195,14 @@
       <c r="Q17" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S17" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1188,8 +1248,14 @@
       <c r="Q18" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1207,8 +1273,10 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1254,8 +1322,14 @@
       <c r="Q20" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1301,8 +1375,14 @@
       <c r="Q21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1348,8 +1428,14 @@
       <c r="Q22" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S22" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1395,8 +1481,14 @@
       <c r="Q23" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S23" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1442,8 +1534,14 @@
       <c r="Q24" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S24" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1489,8 +1587,14 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+      <c r="S25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1536,8 +1640,14 @@
       <c r="Q26" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S26" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1583,8 +1693,14 @@
       <c r="Q27" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S27" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1630,8 +1746,14 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+      <c r="S28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1677,8 +1799,14 @@
       <c r="Q29" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R29" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S29" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1724,8 +1852,14 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+      <c r="S30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1771,8 +1905,14 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+      <c r="S31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1818,8 +1958,14 @@
       <c r="Q32" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -1865,8 +2011,14 @@
       <c r="Q33" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S33" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1912,8 +2064,14 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+      <c r="S34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -1959,60 +2117,72 @@
       <c r="Q35" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S35" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46173</v>
+      </c>
+      <c r="E38" s="2">
+        <v>46081</v>
+      </c>
+      <c r="F38" s="2">
         <v>45991</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45900</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45809</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45717</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45627</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45536</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45445</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45353</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>45263</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>45172</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>45074</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44985</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44892</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44800</v>
       </c>
     </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2030,8 +2200,10 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2049,55 +2221,63 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1030300</v>
+      </c>
+      <c r="E41" s="3">
+        <v>1029000</v>
+      </c>
+      <c r="F41" s="3">
         <v>979600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>999600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>1005000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>938500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>930600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>962600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>950000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>943400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>1121500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>1114900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>1243100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>1221900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>1605200</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>1564300</v>
       </c>
     </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2143,337 +2323,385 @@
       <c r="Q42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R42" s="3">
+        <v>0</v>
+      </c>
+      <c r="S42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>251400</v>
+      </c>
+      <c r="E43" s="3">
+        <v>251100</v>
+      </c>
+      <c r="F43" s="3">
         <v>152500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>155600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>282900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>264100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>195000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>201700</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>505800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>502300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>477700</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>474900</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>380800</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>374300</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>305600</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>297800</v>
       </c>
     </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>48900</v>
+      </c>
+      <c r="E44" s="3">
+        <v>48900</v>
+      </c>
+      <c r="F44" s="3">
         <v>42200</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>43100</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>78200</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>73000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>50600</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>52300</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>157100</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>156000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>161100</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>160100</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>105600</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>103800</v>
       </c>
-      <c r="P44" s="3">
+      <c r="R44" s="3">
         <v>129100</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="S44" s="3">
         <v>125800</v>
       </c>
     </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>7100</v>
+      </c>
+      <c r="E45" s="3">
+        <v>7100</v>
+      </c>
+      <c r="F45" s="3">
         <v>1500</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>1500</v>
       </c>
-      <c r="F45" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G45" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H45" s="3">
+      <c r="H45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J45" s="3">
         <v>745300</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>770900</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>54800</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>54500</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>61700</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>61400</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>1800</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>1800</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>10900</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>10600</v>
       </c>
     </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1337800</v>
+      </c>
+      <c r="E46" s="3">
+        <v>1336200</v>
+      </c>
+      <c r="F46" s="3">
         <v>1239300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>1264600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>1366000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>1275700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>1989200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>2057500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>1667700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>1656100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>1822000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>1811300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>1731400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>1701800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>2143200</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>2088600</v>
       </c>
     </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>1118400</v>
+      </c>
+      <c r="E47" s="3">
+        <v>1117100</v>
+      </c>
+      <c r="F47" s="3">
         <v>1069000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="G47" s="3">
         <v>1090900</v>
       </c>
-      <c r="F47" s="3">
+      <c r="H47" s="3">
         <v>1288100</v>
       </c>
-      <c r="G47" s="3">
+      <c r="I47" s="3">
         <v>1202900</v>
       </c>
-      <c r="H47" s="3">
+      <c r="J47" s="3">
         <v>136100</v>
       </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>140700</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>12300</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>12300</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>12000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>12000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="P47" s="3">
         <v>140300</v>
       </c>
-      <c r="O47" s="3">
+      <c r="Q47" s="3">
         <v>137900</v>
       </c>
-      <c r="P47" s="3">
+      <c r="R47" s="3">
         <v>18900</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="S47" s="3">
         <v>18400</v>
       </c>
     </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1929200</v>
+      </c>
+      <c r="E48" s="3">
+        <v>1926900</v>
+      </c>
+      <c r="F48" s="3">
         <v>2142900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>2186700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>2175900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>2032000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>2312500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>2391900</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>2805800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>2786300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>2817700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>2801000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>2827300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>2779000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>2745900</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>2675900</v>
       </c>
     </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>885300</v>
+      </c>
+      <c r="E49" s="3">
+        <v>884200</v>
+      </c>
+      <c r="F49" s="3">
         <v>881100</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>899100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>903700</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>843900</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>831800</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>860300</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>812700</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>807000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>785700</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>781100</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>709300</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>697100</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>655000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="S49" s="3">
         <v>638300</v>
       </c>
     </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2519,8 +2747,14 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+      <c r="S50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2566,55 +2800,67 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+      <c r="S51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>9400</v>
+      </c>
+      <c r="E52" s="3">
+        <v>9400</v>
+      </c>
+      <c r="F52" s="3">
         <v>8200</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>8400</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>4600</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>4300</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>5200</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>5400</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>138100</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>137100</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>110700</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>110000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>104900</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>103100</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>252600</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>246200</v>
       </c>
     </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2660,55 +2906,67 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+      <c r="S53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>5614100</v>
+      </c>
+      <c r="E54" s="3">
+        <v>5607300</v>
+      </c>
+      <c r="F54" s="3">
         <v>5664200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>5780100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>5922000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>5530300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>5280700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>5462100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>5450600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>5412700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>5613800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>5580600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>5533100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>5438500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>5817900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>5669700</v>
       </c>
     </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2726,8 +2984,10 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2745,290 +3005,328 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>317900</v>
+      </c>
+      <c r="E57" s="3">
+        <v>317500</v>
+      </c>
+      <c r="F57" s="3">
         <v>346700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>353800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>352900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>329600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>313300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>324100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>569500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>565600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>593700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>590200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>547100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>537700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>612000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>596400</v>
       </c>
     </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>507300</v>
+      </c>
+      <c r="E58" s="3">
+        <v>506700</v>
+      </c>
+      <c r="F58" s="3">
         <v>119700</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>122100</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>227500</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>212400</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>38700</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>40100</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>76300</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>75800</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>70300</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>69900</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>73700</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>72500</v>
       </c>
-      <c r="P58" s="3">
+      <c r="R58" s="3">
         <v>83200</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="S58" s="3">
         <v>81000</v>
       </c>
     </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>122400</v>
+      </c>
+      <c r="E59" s="3">
+        <v>122200</v>
+      </c>
+      <c r="F59" s="3">
         <v>154700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>157900</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>72800</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>68000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>703000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>727100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>63900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>63400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>65700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>65300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>81700</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>80300</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>38000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>37000</v>
       </c>
     </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>947600</v>
+      </c>
+      <c r="E60" s="3">
+        <v>946400</v>
+      </c>
+      <c r="F60" s="3">
         <v>621100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>633800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>653200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>610000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>1056100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>1092400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>709700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>704800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>731100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>726800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>702500</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>690500</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>733500</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>714800</v>
       </c>
     </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1829400</v>
+      </c>
+      <c r="E61" s="3">
+        <v>1827100</v>
+      </c>
+      <c r="F61" s="3">
         <v>2247700</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>2293700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>2191100</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>2046200</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>2119000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>2191800</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>2428600</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>2411700</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>2413800</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>2399600</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>2279700</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>2240700</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>2219600</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>2163100</v>
       </c>
     </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>24700</v>
+      </c>
+      <c r="E62" s="3">
+        <v>24600</v>
+      </c>
+      <c r="F62" s="3">
         <v>22800</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>23200</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>23000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>21500</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>21600</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>22300</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>37900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>37700</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>36400</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>36200</v>
-      </c>
-      <c r="N62" s="3">
-        <v>33000</v>
-      </c>
-      <c r="O62" s="3">
-        <v>32500</v>
       </c>
       <c r="P62" s="3">
         <v>33000</v>
       </c>
       <c r="Q62" s="3">
+        <v>32500</v>
+      </c>
+      <c r="R62" s="3">
+        <v>33000</v>
+      </c>
+      <c r="S62" s="3">
         <v>32200</v>
       </c>
     </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3074,8 +3372,14 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+      <c r="S63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3121,8 +3425,14 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+      <c r="S64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3168,55 +3478,67 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+      <c r="S65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>3502100</v>
+      </c>
+      <c r="E66" s="3">
+        <v>3497900</v>
+      </c>
+      <c r="F66" s="3">
         <v>3597500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>3671100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>3563800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>3328000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>3792700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>3923000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>3704700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>3678900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>3698600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>3676700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>3503600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>3443600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>3479800</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>3391200</v>
       </c>
     </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3234,8 +3556,10 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3281,8 +3605,14 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+      <c r="S68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3328,8 +3658,14 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+      <c r="S69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3375,8 +3711,14 @@
       <c r="Q70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+      <c r="S70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3422,55 +3764,67 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+      <c r="S71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-334200</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-333800</v>
+      </c>
+      <c r="F72" s="3">
         <v>-425600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-434300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-183100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-171000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-951300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-984000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-720400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-715400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-570100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-566800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-474800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>-466700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>-204300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>-199100</v>
       </c>
     </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3516,8 +3870,14 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+      <c r="S73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3563,8 +3923,14 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+      <c r="S74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3610,55 +3976,67 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+      <c r="S75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>2111900</v>
+      </c>
+      <c r="E76" s="3">
+        <v>2109400</v>
+      </c>
+      <c r="F76" s="3">
         <v>2066700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>2109000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>2358200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>2202300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>1506400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>1558100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>1737600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>1725500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>1885300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>1874100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>1963900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>1930300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>2221500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>2164900</v>
       </c>
     </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3704,60 +4082,72 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+      <c r="S77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46173</v>
+      </c>
+      <c r="E80" s="2">
+        <v>46081</v>
+      </c>
+      <c r="F80" s="2">
         <v>45991</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45900</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45809</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45717</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45627</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45536</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45445</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45353</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>45263</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>45172</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>45074</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44985</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44892</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44800</v>
       </c>
     </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -3803,8 +4193,14 @@
       <c r="Q81" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S81" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3822,55 +4218,63 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>81500</v>
+      </c>
+      <c r="E83" s="3">
+        <v>76100</v>
+      </c>
+      <c r="F83" s="3">
         <v>90300</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>93400</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>85100</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>84500</v>
       </c>
-      <c r="H83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J83" s="3">
+      <c r="J83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L83" s="3">
         <v>80900</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>79500</v>
       </c>
-      <c r="L83" s="3">
+      <c r="N83" s="3">
         <v>66400</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>64700</v>
       </c>
-      <c r="N83" s="3">
+      <c r="P83" s="3">
         <v>69700</v>
       </c>
-      <c r="O83" s="3">
+      <c r="Q83" s="3">
         <v>74100</v>
       </c>
-      <c r="P83" s="3">
+      <c r="R83" s="3">
         <v>54700</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="S83" s="3">
         <v>56500</v>
       </c>
     </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3916,8 +4320,14 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+      <c r="S84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3963,8 +4373,14 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+      <c r="S85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4010,8 +4426,14 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+      <c r="S86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4057,8 +4479,14 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+      <c r="S87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4104,55 +4532,67 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+      <c r="S88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>128100</v>
+      </c>
+      <c r="E89" s="3">
+        <v>127900</v>
+      </c>
+      <c r="F89" s="3">
         <v>132100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>134800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>95700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>89400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>126900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>131300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>44000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>43700</v>
       </c>
-      <c r="L89" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M89" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N89" s="3">
+      <c r="N89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P89" s="3">
         <v>-10100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>-9900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>1300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4170,55 +4610,63 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-44200</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-44100</v>
+      </c>
+      <c r="F91" s="3">
         <v>-87300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-89100</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-58500</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-54600</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-48500</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-50100</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-76700</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-76100</v>
       </c>
-      <c r="L91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N91" s="3">
+      <c r="N91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P91" s="3">
         <v>-120100</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-118000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="R91" s="3">
         <v>-207300</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="S91" s="3">
         <v>-202000</v>
       </c>
     </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4264,8 +4712,14 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+      <c r="S92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4311,55 +4765,67 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+      <c r="S93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-60400</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-60300</v>
+      </c>
+      <c r="F94" s="3">
         <v>-103600</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-105700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-152300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-142300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-110600</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-114400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-114300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-113500</v>
       </c>
-      <c r="L94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N94" s="3">
+      <c r="N94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P94" s="3">
         <v>-166600</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-163700</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-202600</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>-197500</v>
       </c>
     </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4377,8 +4843,10 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4424,8 +4892,14 @@
       <c r="Q96" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S96" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4471,8 +4945,14 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+      <c r="S97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4518,8 +4998,14 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+      <c r="S98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4565,145 +5051,169 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+      <c r="S99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-47700</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-47600</v>
+      </c>
+      <c r="F100" s="3">
         <v>-32200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-32800</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>42700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>39900</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>1300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>1400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-16800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-16700</v>
       </c>
-      <c r="L100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N100" s="3">
+      <c r="N100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P100" s="3">
         <v>-16300</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>-16100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>343500</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>334800</v>
       </c>
     </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-3400</v>
+      </c>
+      <c r="E101" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="F101" s="3">
         <v>-1800</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>-1900</v>
       </c>
-      <c r="F101" s="3">
+      <c r="H101" s="3">
         <v>-800</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>-800</v>
       </c>
-      <c r="H101" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I101" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J101" s="3">
+      <c r="J101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L101" s="3">
         <v>-3900</v>
       </c>
-      <c r="K101" s="3">
+      <c r="M101" s="3">
         <v>-3800</v>
       </c>
-      <c r="L101" s="3">
+      <c r="N101" s="3">
         <v>6000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="O101" s="3">
         <v>5900</v>
       </c>
-      <c r="N101" s="3">
+      <c r="P101" s="3">
         <v>7400</v>
       </c>
-      <c r="O101" s="3">
+      <c r="Q101" s="3">
         <v>7900</v>
       </c>
-      <c r="P101" s="3">
+      <c r="R101" s="3">
         <v>17400</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="S101" s="3">
         <v>18000</v>
       </c>
     </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>16600</v>
+      </c>
+      <c r="E102" s="3">
+        <v>16600</v>
+      </c>
+      <c r="F102" s="3">
         <v>-3800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-3800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-17300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-16200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>15800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>16400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-87900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-87300</v>
       </c>
-      <c r="L102" s="3">
-        <v>0</v>
-      </c>
-      <c r="M102" s="3">
-        <v>0</v>
-      </c>
       <c r="N102" s="3">
+        <v>0</v>
+      </c>
+      <c r="O102" s="3">
+        <v>0</v>
+      </c>
+      <c r="P102" s="3">
         <v>-196900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>-193500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>148300</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>144500</v>
       </c>
     </row>
